--- a/tests/v1/fixtures/office6m/2026-09/bank_statements/HB_HOLD_USD_2026-08.xlsx
+++ b/tests/v1/fixtures/office6m/2026-09/bank_statements/HB_HOLD_USD_2026-08.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -581,31 +581,31 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BF-HB-HOLD-USD-08</t>
+          <t>TT-7741XQ</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>bank_fee</t>
+          <t>transfer_in</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Account maintenance fee</t>
+          <t>TT IN REF 7741XQ - remitter name not stated</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Harbour Bank (synthetic)</t>
+          <t>Unknown remitter</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>-48.1</v>
+        <v>48250</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -616,33 +616,68 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>BF-HB-HOLD-USD-08</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>bank_fee</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Account maintenance fee</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Harbour Bank (synthetic)</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>-48.1</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>IN-HB-HOLD-USD-08</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>interest</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>Credit interest</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Harbour Bank (synthetic)</t>
         </is>
       </c>
-      <c r="F6" t="n">
+      <c r="F7" t="n">
         <v>52.2</v>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
@@ -719,13 +754,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>596959.9</v>
+        <v>723709.9</v>
       </c>
       <c r="E2" t="n">
-        <v>455410.17</v>
+        <v>355410.17</v>
       </c>
       <c r="F2" t="n">
-        <v>1052370.07</v>
+        <v>1079120.07</v>
       </c>
     </row>
     <row r="3">
@@ -745,13 +780,13 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1052370.07</v>
+        <v>1079120.07</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>1052370.07</v>
+        <v>1079120.07</v>
       </c>
     </row>
     <row r="4">
@@ -771,13 +806,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1052370.07</v>
+        <v>1079120.07</v>
       </c>
       <c r="E4" t="n">
         <v>600000</v>
       </c>
       <c r="F4" t="n">
-        <v>1652370.07</v>
+        <v>1679120.07</v>
       </c>
     </row>
     <row r="5">
@@ -797,13 +832,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1652370.07</v>
+        <v>1679120.07</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>1652370.07</v>
+        <v>1679120.07</v>
       </c>
     </row>
     <row r="6">
@@ -823,13 +858,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1652370.07</v>
+        <v>1679120.07</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>1652370.07</v>
+        <v>1679120.07</v>
       </c>
     </row>
     <row r="7">
@@ -849,13 +884,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1652370.07</v>
+        <v>1679120.07</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>1652370.07</v>
+        <v>1679120.07</v>
       </c>
     </row>
     <row r="8">
@@ -875,13 +910,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1652370.07</v>
+        <v>1679120.07</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>1652370.07</v>
+        <v>1679120.07</v>
       </c>
     </row>
     <row r="9">
@@ -901,13 +936,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1652370.07</v>
+        <v>1679120.07</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>1652370.07</v>
+        <v>1679120.07</v>
       </c>
     </row>
     <row r="10">
@@ -927,13 +962,13 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1652370.07</v>
+        <v>1679120.07</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>1652370.07</v>
+        <v>1679120.07</v>
       </c>
     </row>
     <row r="11">
@@ -953,13 +988,13 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1652370.07</v>
+        <v>1679120.07</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>1652370.07</v>
+        <v>1679120.07</v>
       </c>
     </row>
     <row r="12">
@@ -979,13 +1014,13 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1652370.07</v>
+        <v>1679120.07</v>
       </c>
       <c r="E12" t="n">
         <v>-22500</v>
       </c>
       <c r="F12" t="n">
-        <v>1629870.07</v>
+        <v>1656620.07</v>
       </c>
     </row>
     <row r="13">
@@ -1005,13 +1040,13 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1629870.07</v>
+        <v>1656620.07</v>
       </c>
       <c r="E13" t="n">
         <v>-600000</v>
       </c>
       <c r="F13" t="n">
-        <v>1029870.07</v>
+        <v>1056620.07</v>
       </c>
     </row>
     <row r="14">
@@ -1031,13 +1066,13 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1029870.07</v>
+        <v>1056620.07</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>48250</v>
       </c>
       <c r="F14" t="n">
-        <v>1029870.07</v>
+        <v>1104870.07</v>
       </c>
     </row>
     <row r="15">
@@ -1057,13 +1092,13 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1029870.07</v>
+        <v>1104870.07</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>1029870.07</v>
+        <v>1104870.07</v>
       </c>
     </row>
     <row r="16">
@@ -1083,13 +1118,13 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1029870.07</v>
+        <v>1104870.07</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>1029870.07</v>
+        <v>1104870.07</v>
       </c>
     </row>
     <row r="17">
@@ -1109,13 +1144,13 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1029870.07</v>
+        <v>1104870.07</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>1029870.07</v>
+        <v>1104870.07</v>
       </c>
     </row>
     <row r="18">
@@ -1135,13 +1170,13 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1029870.07</v>
+        <v>1104870.07</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>1029870.07</v>
+        <v>1104870.07</v>
       </c>
     </row>
     <row r="19">
@@ -1161,13 +1196,13 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1029870.07</v>
+        <v>1104870.07</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>1029870.07</v>
+        <v>1104870.07</v>
       </c>
     </row>
     <row r="20">
@@ -1187,13 +1222,13 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1029870.07</v>
+        <v>1104870.07</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>1029870.07</v>
+        <v>1104870.07</v>
       </c>
     </row>
     <row r="21">
@@ -1213,13 +1248,13 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1029870.07</v>
+        <v>1104870.07</v>
       </c>
       <c r="E21" t="n">
         <v>-48.1</v>
       </c>
       <c r="F21" t="n">
-        <v>1029821.97</v>
+        <v>1104821.97</v>
       </c>
     </row>
     <row r="22">
@@ -1239,13 +1274,13 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1029821.97</v>
+        <v>1104821.97</v>
       </c>
       <c r="E22" t="n">
         <v>52.2</v>
       </c>
       <c r="F22" t="n">
-        <v>1029874.17</v>
+        <v>1104874.17</v>
       </c>
     </row>
   </sheetData>
